--- a/01_Reporting_Suite/Coates_K2_MyGear_Art_Brief.xlsx
+++ b/01_Reporting_Suite/Coates_K2_MyGear_Art_Brief.xlsx
@@ -506,7 +506,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Built 05 Aug 2026 by walking the live pages and the art folder on this machine - 80 named surfaces. The rule this workbook serves: IF IT HAS A NAME, IT HAS A PICTURE. Tools and consumables live in their own workbook (Coates_K2_Thumbnail_Upgrade_Brief.xlsx); this is everything else.</t>
+          <t>Built 08 Aug 2026 by walking the live pages and the art folder on this machine - 80 named surfaces. The rule this workbook serves: IF IT HAS A NAME, IT HAS A PICTURE. Tools and consumables live in their own workbook (Coates_K2_Thumbnail_Upgrade_Brief.xlsx); this is everything else.</t>
         </is>
       </c>
     </row>
